--- a/src/test/resources/Details_chrome.xlsx
+++ b/src/test/resources/Details_chrome.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497760\projects\IdentifyNewBikes\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8547997E-1E8E-4027-BC3D-5500CC6DD5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9DC01B-DB6C-4FC2-A670-1E49140EE742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="218">
   <si>
     <t>Bike Name</t>
   </si>
@@ -145,501 +145,504 @@
     <t>Rs. 6.00 Lakh</t>
   </si>
   <si>
+    <t>Honda City i VTEC CVT SV</t>
+  </si>
+  <si>
+    <t>Rs. 5.27 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.90 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC V</t>
+  </si>
+  <si>
+    <t>Rs. 6.75 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT</t>
+  </si>
+  <si>
+    <t>Rs. 6.70 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT Exclusive</t>
+  </si>
+  <si>
+    <t>Rs. 7.52 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City SV MT</t>
+  </si>
+  <si>
+    <t>Rs. 5.15 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.35 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC E</t>
+  </si>
+  <si>
+    <t>Rs. 5.99 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i DTec E</t>
+  </si>
+  <si>
+    <t>Rs. 5.85 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.75 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI BSVI</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT</t>
+  </si>
+  <si>
+    <t>Rs. 9.13 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI</t>
+  </si>
+  <si>
+    <t>Rs. 5.55 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX Plus</t>
+  </si>
+  <si>
+    <t>Rs. 11.23 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.80 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT ZXI BSIV</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXI Plus DT AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 7.63 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT VX</t>
+  </si>
+  <si>
+    <t>Rs. 7.75 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI</t>
+  </si>
+  <si>
+    <t>Rs. 5.30 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.76 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX CVT 2 Airbag</t>
+  </si>
+  <si>
+    <t>Rs. 11.90 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI AMT BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.12 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V AT</t>
+  </si>
+  <si>
+    <t>Rs. 5.98 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI</t>
+  </si>
+  <si>
+    <t>Rs. 6.40 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.16 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift LXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.75 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.1L</t>
+  </si>
+  <si>
+    <t>Rs. 3.91 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna</t>
+  </si>
+  <si>
+    <t>Rs. 3.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.58 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz</t>
+  </si>
+  <si>
+    <t>Rs. 2.10 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 4.66 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VDI BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 3.75 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.80 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus AMT</t>
+  </si>
+  <si>
+    <t>Rs. 9.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City ZX MT</t>
+  </si>
+  <si>
+    <t>Rs. 16.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 V MT</t>
+  </si>
+  <si>
+    <t>Rs. 8.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 8.79 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City CVT</t>
+  </si>
+  <si>
+    <t>Rs. 17.60 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City VX MT</t>
+  </si>
+  <si>
+    <t>Rs. 7.80 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 FWD</t>
+  </si>
+  <si>
+    <t>Rs. 7.49 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna 1.1</t>
+  </si>
+  <si>
+    <t>Rs. 3.10 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.96 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Magna 1.2</t>
+  </si>
+  <si>
+    <t>Rs. 2.25 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 13.00 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Asta</t>
+  </si>
+  <si>
+    <t>Rs. 2.45 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 4.20 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXI BSVI</t>
+  </si>
+  <si>
+    <t>Rs. 6.80 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.30 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 5.45 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.59 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZXi Plus</t>
+  </si>
+  <si>
+    <t>Rs. 6.25 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC CVT ZX</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 EXI S</t>
+  </si>
+  <si>
+    <t>Rs. 2.65 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.0 G1</t>
+  </si>
+  <si>
+    <t>Rs. 5.90 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 9.90 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W11 AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 11.47 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS III</t>
+  </si>
+  <si>
+    <t>Rs. 3.40 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 2.8 2WD AT BSIV</t>
+  </si>
+  <si>
+    <t>Rs. 27.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.25 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.15 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W8 2WD</t>
+  </si>
+  <si>
+    <t>Honda City i VTEC S</t>
+  </si>
+  <si>
+    <t>Rs. 4.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 VX (Diesel) 8 Seater</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 GXI</t>
+  </si>
+  <si>
+    <t>Rs. 1.60 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 26.50 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS IV</t>
+  </si>
+  <si>
+    <t>Rs. 15.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.75 Lakh</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner 4x4 AT</t>
+  </si>
+  <si>
+    <t>Rs. 22.00 Lakh</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 W10 2WD</t>
+  </si>
+  <si>
+    <t>Rs. 7.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 16.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 7.20 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 12.50 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 15.00 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 6.99 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 2.50 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V</t>
+  </si>
+  <si>
+    <t>Rs. 10.01 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.76 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC ZX</t>
+  </si>
+  <si>
+    <t>Rs. 11.00 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City V MT AVN</t>
+  </si>
+  <si>
+    <t>Rs. 4.35 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 3.45 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift ZDi</t>
+  </si>
+  <si>
+    <t>Rs. 4.55 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai Santro Xing XO eRLX Euro II</t>
+  </si>
+  <si>
+    <t>Rs. 1.85 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VVT VXI</t>
+  </si>
+  <si>
+    <t>Rs. 4.10 Lakh</t>
+  </si>
+  <si>
+    <t>Hyundai i10 Sportz 1.2 AT</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 R W10 FWD</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500 AT W10 AWD</t>
+  </si>
+  <si>
+    <t>Rs. 11.75 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift VXi</t>
+  </si>
+  <si>
+    <t>Rs. 6.95 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 10.48 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City i-VTEC S</t>
+  </si>
+  <si>
+    <t>Honda City i DTEC SV</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S AT</t>
+  </si>
+  <si>
+    <t>Rs. 3.85 Lakh</t>
+  </si>
+  <si>
+    <t>Honda City 1.5 S MT</t>
+  </si>
+  <si>
+    <t>Rs. 4.60 Lakh</t>
+  </si>
+  <si>
+    <t>Maruti Swift AMT VXI</t>
+  </si>
+  <si>
+    <t>Honda City V Apex Edition CVT</t>
+  </si>
+  <si>
+    <t>Rs. 14.90 Lakh</t>
+  </si>
+  <si>
+    <t>Rs. 9.84 Lakh</t>
+  </si>
+  <si>
     <t>Honda City i-VTEC CVT V</t>
   </si>
   <si>
     <t>Rs. 8.00 Lakh</t>
   </si>
   <si>
-    <t>Honda City V MT</t>
-  </si>
-  <si>
-    <t>Rs. 9.75 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift LXI BSVI</t>
-  </si>
-  <si>
-    <t>Maruti Swift AMT ZXI</t>
-  </si>
-  <si>
-    <t>Rs. 5.55 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City ZX CVT</t>
-  </si>
-  <si>
-    <t>Rs. 9.13 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City ZX Plus</t>
-  </si>
-  <si>
-    <t>Rs. 11.23 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 9.80 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift AMT ZXI BSIV</t>
-  </si>
-  <si>
-    <t>Maruti Swift ZXI Plus DT AMT BSVI</t>
-  </si>
-  <si>
-    <t>Rs. 7.63 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift VXI</t>
-  </si>
-  <si>
-    <t>Rs. 5.30 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i-VTEC CVT VX</t>
-  </si>
-  <si>
-    <t>Rs. 7.75 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 7.76 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift ZDI BSIV</t>
-  </si>
-  <si>
-    <t>Rs. 4.66 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift VDI BSIV</t>
-  </si>
-  <si>
-    <t>Rs. 3.75 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift VDI</t>
-  </si>
-  <si>
-    <t>Rs. 3.80 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift ZXi Plus AMT</t>
-  </si>
-  <si>
-    <t>Rs. 9.25 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 V MT</t>
-  </si>
-  <si>
-    <t>Rs. 8.20 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City ZX MT</t>
-  </si>
-  <si>
-    <t>Rs. 16.50 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i-VTEC VX</t>
-  </si>
-  <si>
-    <t>Rs. 6.50 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City CVT</t>
-  </si>
-  <si>
-    <t>Rs. 17.60 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 8.79 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City VX MT</t>
-  </si>
-  <si>
-    <t>Rs. 7.80 Lakh</t>
-  </si>
-  <si>
-    <t>Mahindra XUV500 W8 FWD</t>
-  </si>
-  <si>
-    <t>Rs. 7.49 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 4.96 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Magna 1.1</t>
-  </si>
-  <si>
-    <t>Rs. 3.10 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Magna 1.2</t>
-  </si>
-  <si>
-    <t>Rs. 2.25 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift VXI BSVI</t>
-  </si>
-  <si>
-    <t>Rs. 6.80 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Asta</t>
-  </si>
-  <si>
-    <t>Rs. 2.45 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 4.20 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 6.30 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 13.00 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift LXI</t>
-  </si>
-  <si>
-    <t>Rs. 5.45 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 3.59 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift ZXi Plus</t>
-  </si>
-  <si>
-    <t>Rs. 7.50 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 6.25 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i-VTEC CVT ZX</t>
-  </si>
-  <si>
-    <t>Rs. 4.80 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 EXI S</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Sportz</t>
-  </si>
-  <si>
-    <t>Rs. 2.65 Lakh</t>
-  </si>
-  <si>
-    <t>Toyota Innova 2.0 G1</t>
-  </si>
-  <si>
-    <t>Rs. 5.90 Lakh</t>
-  </si>
-  <si>
-    <t>Toyota Innova 2.5 VX (Diesel) 7 Seater BS IV</t>
-  </si>
-  <si>
-    <t>Rs. 9.90 Lakh</t>
-  </si>
-  <si>
-    <t>Mahindra XUV500 W11 AT BSIV</t>
-  </si>
-  <si>
-    <t>Rs. 11.47 Lakh</t>
-  </si>
-  <si>
-    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS III</t>
-  </si>
-  <si>
-    <t>Rs. 3.40 Lakh</t>
-  </si>
-  <si>
-    <t>Toyota Fortuner 2.8 2WD AT BSIV</t>
-  </si>
-  <si>
-    <t>Rs. 27.00 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Magna</t>
-  </si>
-  <si>
-    <t>Rs. 3.25 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 3.15 Lakh</t>
-  </si>
-  <si>
-    <t>Mahindra XUV500 W8 2WD</t>
-  </si>
-  <si>
-    <t>Honda City i VTEC S</t>
-  </si>
-  <si>
-    <t>Rs. 4.50 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 10.50 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 9.50 Lakh</t>
-  </si>
-  <si>
-    <t>Toyota Innova 2.5 VX (Diesel) 8 Seater</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 GXI</t>
-  </si>
-  <si>
-    <t>Rs. 1.60 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 26.50 Lakh</t>
-  </si>
-  <si>
-    <t>Toyota Innova 2.5 G (Diesel) 7 Seater BS IV</t>
-  </si>
-  <si>
-    <t>Rs. 15.90 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 10.75 Lakh</t>
-  </si>
-  <si>
-    <t>Toyota Fortuner 4x4 AT</t>
-  </si>
-  <si>
-    <t>Rs. 22.00 Lakh</t>
-  </si>
-  <si>
-    <t>Mahindra XUV500 W10 2WD</t>
-  </si>
-  <si>
-    <t>Rs. 7.00 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 16.00 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i-VTEC V</t>
-  </si>
-  <si>
-    <t>Rs. 7.20 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 12.50 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 15.00 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i VTEC V</t>
-  </si>
-  <si>
-    <t>Rs. 6.99 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 V MT Exclusive</t>
-  </si>
-  <si>
-    <t>Rs. 6.90 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City SV MT</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 V AT</t>
-  </si>
-  <si>
-    <t>Rs. 2.50 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City V</t>
-  </si>
-  <si>
-    <t>Rs. 10.01 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 9.76 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i-VTEC ZX</t>
-  </si>
-  <si>
-    <t>Rs. 11.00 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City V MT AVN</t>
-  </si>
-  <si>
-    <t>Rs. 4.35 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 3.45 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift ZDi</t>
-  </si>
-  <si>
-    <t>Rs. 4.55 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai Santro Xing XO eRLX Euro II</t>
-  </si>
-  <si>
-    <t>Rs. 1.85 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift VVT VXI</t>
-  </si>
-  <si>
-    <t>Rs. 4.10 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Sportz 1.2 AT</t>
-  </si>
-  <si>
-    <t>Mahindra XUV500 R W10 FWD</t>
-  </si>
-  <si>
-    <t>Mahindra XUV500 AT W10 AWD</t>
-  </si>
-  <si>
-    <t>Rs. 11.75 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift VXi</t>
-  </si>
-  <si>
-    <t>Rs. 6.95 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 10.48 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i-VTEC S</t>
-  </si>
-  <si>
-    <t>Honda City i VTEC CVT SV</t>
-  </si>
-  <si>
-    <t>Rs. 5.27 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i VTEC CVT VX</t>
-  </si>
-  <si>
-    <t>Rs. 7.25 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 6.75 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 6.70 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 5.60 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 7.52 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 5.15 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 6.35 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i DTEC E</t>
-  </si>
-  <si>
-    <t>Rs. 5.99 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i DTec E</t>
-  </si>
-  <si>
-    <t>Rs. 5.85 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City i DTEC SV</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 S AT</t>
-  </si>
-  <si>
-    <t>Rs. 3.85 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City 1.5 S MT</t>
-  </si>
-  <si>
-    <t>Rs. 4.60 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift AMT VXI</t>
-  </si>
-  <si>
-    <t>Rs. 8.90 Lakh</t>
-  </si>
-  <si>
-    <t>Honda City V Apex Edition CVT</t>
-  </si>
-  <si>
-    <t>Rs. 14.90 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 9.84 Lakh</t>
-  </si>
-  <si>
     <t>Honda City VX CVT</t>
   </si>
   <si>
     <t>Rs. 9.24 Lakh</t>
   </si>
   <si>
-    <t>Honda City ZX CVT 2 Airbag</t>
-  </si>
-  <si>
-    <t>Rs. 11.90 Lakh</t>
-  </si>
-  <si>
-    <t>Maruti Swift VXI AMT BSVI</t>
-  </si>
-  <si>
-    <t>Rs. 6.12 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 6.40 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 3.20 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 5.98 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 4.75 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 5.16 Lakh</t>
-  </si>
-  <si>
-    <t>Hyundai i10 Sportz 1.1L</t>
-  </si>
-  <si>
-    <t>Rs. 3.91 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 3.58 Lakh</t>
-  </si>
-  <si>
     <t>Maruti Swift ZXI</t>
   </si>
   <si>
@@ -649,21 +652,18 @@
     <t>Rs. 4.06 Lakh</t>
   </si>
   <si>
-    <t>Rs. 2.10 Lakh</t>
-  </si>
-  <si>
     <t>Hyundai i10 Sportz AT</t>
   </si>
   <si>
     <t>Rs. 2.70 Lakh</t>
   </si>
   <si>
+    <t>Rs. 3.65 Lakh</t>
+  </si>
+  <si>
     <t>Honda City i DTEC S</t>
   </si>
   <si>
-    <t>Rs. 3.65 Lakh</t>
-  </si>
-  <si>
     <t>Rs. 4.45 Lakh</t>
   </si>
   <si>
@@ -676,10 +676,10 @@
     <t>Rs. 2.95 Lakh</t>
   </si>
   <si>
+    <t>Rs. 3.90 Lakh</t>
+  </si>
+  <si>
     <t>Rs. 3.95 Lakh</t>
-  </si>
-  <si>
-    <t>Rs. 3.90 Lakh</t>
   </si>
   <si>
     <t>Car Name</t>
@@ -1010,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1417,600 +1417,6 @@
         <v>37</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C40" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C41" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C42" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C45" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C46" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C47" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C48" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C49" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C50" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C51" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C52" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B53" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C53" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="B54" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C54" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="C55" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C56" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C57" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C58" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B59" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C59" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C60" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B61" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C62" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B63" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C63" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B64" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C64" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B65" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C65" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C66" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C67" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B68" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C68" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B69" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C69" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="B70" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C70" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B71" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C71" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="B72" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C72" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B73" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="C73" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B74" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C74" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B75" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C75" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C76" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B77" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C77" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B78" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C78" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B79" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="C79" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B80" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C80" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B81" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C81" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B82" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C82" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B83" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C83" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B84" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C84" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B85" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C85" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B86" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C86" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B87" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C87" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="B88" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C88" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B89" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C89" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="B90" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C90" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="C91" t="s" s="0">
         <v>11</v>
       </c>
     </row>
@@ -2021,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2230,600 +1636,6 @@
         <v>30</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C30" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C32" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C33" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C34" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C35" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C36" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C37" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C41" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C42" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C45" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C46" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C47" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C48" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C49" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C50" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C51" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C52" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B53" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C53" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B54" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C54" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C55" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C56" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C57" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C58" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B59" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C59" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C60" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B61" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C61" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C62" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B63" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C63" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B64" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C64" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B65" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C65" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C66" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C67" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B68" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C68" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B69" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C69" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B70" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C70" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B71" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="C71" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B72" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C72" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="B73" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C73" t="s" s="0">
         <v>11</v>
       </c>
     </row>
@@ -2834,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B244"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2858,92 +1670,92 @@
         <v>42</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>61</v>
@@ -2954,132 +1766,132 @@
         <v>62</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s" s="0">
         <v>64</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s" s="0">
         <v>66</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s" s="0">
         <v>68</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>90</v>
@@ -3095,7 +1907,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>93</v>
@@ -3103,23 +1915,23 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>61</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>96</v>
@@ -3130,196 +1942,196 @@
         <v>97</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>71</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>130</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>119</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>131</v>
@@ -3327,23 +2139,23 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>134</v>
@@ -3351,39 +2163,39 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>54</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>142</v>
@@ -3399,26 +2211,26 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>147</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74">
@@ -3431,7 +2243,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>150</v>
@@ -3439,50 +2251,50 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B76" t="s" s="0">
         <v>151</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>152</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>101</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B81" t="s" s="0">
         <v>158</v>
-      </c>
-      <c r="B81" t="s" s="0">
-        <v>118</v>
       </c>
     </row>
     <row r="82">
@@ -3503,7 +2315,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>163</v>
@@ -3511,162 +2323,162 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>139</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>95</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>170</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="B93" t="s" s="0">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="B95" t="s" s="0">
-        <v>173</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B97" t="s" s="0">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>179</v>
+        <v>51</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>92</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="B101" t="s" s="0">
         <v>180</v>
-      </c>
-      <c r="B101" t="s" s="0">
-        <v>181</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="B102" t="s" s="0">
         <v>182</v>
-      </c>
-      <c r="B102" t="s" s="0">
-        <v>183</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105">
@@ -3674,111 +2486,111 @@
         <v>184</v>
       </c>
       <c r="B105" t="s" s="0">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s" s="0">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B108" t="s" s="0">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="B109" t="s" s="0">
-        <v>185</v>
+        <v>47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B110" t="s" s="0">
-        <v>190</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="B111" t="s" s="0">
-        <v>192</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>193</v>
+        <v>40</v>
       </c>
       <c r="B112" t="s" s="0">
-        <v>194</v>
+        <v>41</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B113" t="s" s="0">
-        <v>195</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="B114" t="s" s="0">
-        <v>196</v>
+        <v>45</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="B115" t="s" s="0">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B116" t="s" s="0">
-        <v>198</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="B117" t="s" s="0">
-        <v>199</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="B118" t="s" s="0">
-        <v>201</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119">
@@ -3786,52 +2598,52 @@
         <v>53</v>
       </c>
       <c r="B119" t="s" s="0">
-        <v>98</v>
+        <v>54</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B120" t="s" s="0">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B121" t="s" s="0">
-        <v>202</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>203</v>
+        <v>58</v>
       </c>
       <c r="B122" t="s" s="0">
-        <v>204</v>
+        <v>59</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B123" t="s" s="0">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B124" t="s" s="0">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B125" t="s" s="0">
         <v>37</v>
@@ -3839,39 +2651,39 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B126" t="s" s="0">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B127" t="s" s="0">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B128" t="s" s="0">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B129" t="s" s="0">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B130" t="s" s="0">
         <v>10</v>
@@ -3879,202 +2691,202 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B131" t="s" s="0">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="B133" t="s" s="0">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B134" t="s" s="0">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="B135" t="s" s="0">
-        <v>205</v>
+        <v>50</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="B136" t="s" s="0">
-        <v>206</v>
+        <v>128</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B137" t="s" s="0">
-        <v>208</v>
+        <v>193</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B138" t="s" s="0">
-        <v>92</v>
+        <v>195</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="B139" t="s" s="0">
-        <v>113</v>
+        <v>178</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="B140" t="s" s="0">
-        <v>210</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="B141" t="s" s="0">
-        <v>211</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="0">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="B142" t="s" s="0">
-        <v>212</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="0">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B143" t="s" s="0">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="0">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="B144" t="s" s="0">
-        <v>215</v>
+        <v>199</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>62</v>
+        <v>200</v>
       </c>
       <c r="B145" t="s" s="0">
-        <v>156</v>
+        <v>201</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="B146" t="s" s="0">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B148" t="s" s="0">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B149" t="s" s="0">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="B150" t="s" s="0">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B151" t="s" s="0">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="0">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="B152" t="s" s="0">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B153" t="s" s="0">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B154" t="s" s="0">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B155" t="s" s="0">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="156">
@@ -4082,119 +2894,119 @@
         <v>75</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>76</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>81</v>
+        <v>205</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>83</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>85</v>
+        <v>208</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B162" t="s" s="0">
-        <v>87</v>
+        <v>145</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B163" t="s" s="0">
-        <v>88</v>
+        <v>209</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="B164" t="s" s="0">
-        <v>89</v>
+        <v>128</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="B165" t="s" s="0">
-        <v>90</v>
+        <v>211</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>92</v>
+        <v>212</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="B167" t="s" s="0">
-        <v>93</v>
+        <v>214</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B168" t="s" s="0">
-        <v>61</v>
+        <v>215</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B169" t="s" s="0">
-        <v>95</v>
+        <v>216</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="B170" t="s" s="0">
-        <v>96</v>
+        <v>182</v>
       </c>
     </row>
     <row r="171">
@@ -4202,196 +3014,196 @@
         <v>97</v>
       </c>
       <c r="B171" t="s" s="0">
-        <v>71</v>
+        <v>98</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="B172" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B173" t="s" s="0">
-        <v>83</v>
+        <v>101</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B174" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B175" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B176" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="0">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="B177" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="0">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B178" t="s" s="0">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="0">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B179" t="s" s="0">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="0">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B180" t="s" s="0">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="0">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B181" t="s" s="0">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="0">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B182" t="s" s="0">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="0">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B183" t="s" s="0">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="0">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B184" t="s" s="0">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="0">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B185" t="s" s="0">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="0">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B186" t="s" s="0">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="0">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="B187" t="s" s="0">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="0">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B188" t="s" s="0">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="0">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="B189" t="s" s="0">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="0">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="B190" t="s" s="0">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="0">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="B191" t="s" s="0">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="0">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="B192" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B193" t="s" s="0">
-        <v>130</v>
+        <v>47</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="0">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="B194" t="s" s="0">
-        <v>119</v>
+        <v>93</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="0">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="B195" t="s" s="0">
         <v>131</v>
@@ -4399,23 +3211,23 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="0">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B196" t="s" s="0">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B197" t="s" s="0">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="0">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="B198" t="s" s="0">
         <v>134</v>
@@ -4423,39 +3235,39 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B199" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B200" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B201" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B202" t="s" s="0">
-        <v>54</v>
+        <v>136</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="0">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="B203" t="s" s="0">
         <v>142</v>
@@ -4471,26 +3283,26 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="0">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B205" t="s" s="0">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="0">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B206" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B207" t="s" s="0">
-        <v>147</v>
+        <v>47</v>
       </c>
     </row>
     <row r="208">
@@ -4503,7 +3315,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="0">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="B209" t="s" s="0">
         <v>150</v>
@@ -4511,50 +3323,50 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B210" t="s" s="0">
         <v>151</v>
-      </c>
-      <c r="B210" t="s" s="0">
-        <v>152</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="0">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B211" t="s" s="0">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="0">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B212" t="s" s="0">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="0">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B213" t="s" s="0">
-        <v>101</v>
+        <v>155</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="0">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="B214" t="s" s="0">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B215" t="s" s="0">
         <v>158</v>
-      </c>
-      <c r="B215" t="s" s="0">
-        <v>118</v>
       </c>
     </row>
     <row r="216">
@@ -4575,7 +3387,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="0">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="B218" t="s" s="0">
         <v>163</v>
@@ -4583,18 +3395,210 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="0">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B219" t="s" s="0">
-        <v>95</v>
+        <v>151</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="0">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B220" t="s" s="0">
-        <v>119</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B221" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B222" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B223" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B224" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B225" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B226" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B227" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B228" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B229" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B230" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="B231" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B232" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B233" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B234" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="B235" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="B236" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B237" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B238" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="B239" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B240" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="B241" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B242" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="B243" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="B244" t="s" s="0">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4604,7 +3608,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -4614,107 +3618,112 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>86</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>121</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>153</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>112</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>207</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>82</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>86</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>100</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>121</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>153</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>112</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
